--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D506"/>
+  <dimension ref="A1:D509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9538,6 +9538,60 @@
         <v>396.47</v>
       </c>
       <c r="D506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>396.15</v>
+      </c>
+      <c r="C507" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>396.64</v>
+      </c>
+      <c r="C508" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>397.25</v>
+      </c>
+      <c r="C509" t="n">
+        <v>398.33</v>
+      </c>
+      <c r="D509" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9554,7 +9608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15767,6 +15821,36 @@
       </c>
       <c r="B621" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -15935,28 +16019,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1081230486035387</v>
+        <v>0.1213261020586106</v>
       </c>
       <c r="J2" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K2" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007188448001179459</v>
+        <v>0.00904228938279017</v>
       </c>
       <c r="M2" t="n">
-        <v>8.492017517588316</v>
+        <v>8.533237300074628</v>
       </c>
       <c r="N2" t="n">
-        <v>102.3660590161913</v>
+        <v>102.7808515673816</v>
       </c>
       <c r="O2" t="n">
-        <v>10.11761132956744</v>
+        <v>10.138089147733</v>
       </c>
       <c r="P2" t="n">
-        <v>380.5948179912073</v>
+        <v>380.4676266075192</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16013,28 +16097,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0730582650128524</v>
+        <v>0.0823447366636607</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003493521170616409</v>
+        <v>0.00445872742942266</v>
       </c>
       <c r="M3" t="n">
-        <v>8.212108596008337</v>
+        <v>8.230620938481158</v>
       </c>
       <c r="N3" t="n">
-        <v>96.52575085031273</v>
+        <v>96.45995121631046</v>
       </c>
       <c r="O3" t="n">
-        <v>9.824751948538585</v>
+        <v>9.821402711237864</v>
       </c>
       <c r="P3" t="n">
-        <v>386.9750701996861</v>
+        <v>386.8856100941272</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16072,7 +16156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D506"/>
+  <dimension ref="A1:D509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27207,6 +27291,72 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-35.00745045283195,173.77696435040565</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-35.00738025107752,173.7778586588482</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-35.007446048868125,173.7769639186636</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-35.00737395970439,173.77785804203026</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-35.007440566382535,173.77696338118886</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-35.0073754876093,173.77785819182887</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D509"/>
+  <dimension ref="A1:D511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9592,6 +9592,42 @@
         <v>398.33</v>
       </c>
       <c r="D509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>397.98</v>
+      </c>
+      <c r="C510" t="n">
+        <v>398.48</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>398.36</v>
+      </c>
+      <c r="C511" t="n">
+        <v>399.15</v>
+      </c>
+      <c r="D511" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9608,7 +9644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B624"/>
+  <dimension ref="A1:B626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15851,6 +15887,26 @@
       </c>
       <c r="B624" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -16019,28 +16075,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1213261020586106</v>
+        <v>0.1309213533184835</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00904228938279017</v>
+        <v>0.0105056986892994</v>
       </c>
       <c r="M2" t="n">
-        <v>8.533237300074628</v>
+        <v>8.565481048043436</v>
       </c>
       <c r="N2" t="n">
-        <v>102.7808515673816</v>
+        <v>103.1935048242156</v>
       </c>
       <c r="O2" t="n">
-        <v>10.138089147733</v>
+        <v>10.15842039020908</v>
       </c>
       <c r="P2" t="n">
-        <v>380.4676266075192</v>
+        <v>380.3748252679683</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16097,28 +16153,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0823447366636607</v>
+        <v>0.08880004966238128</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00445872742942266</v>
+        <v>0.005198739123882468</v>
       </c>
       <c r="M3" t="n">
-        <v>8.230620938481158</v>
+        <v>8.24446545721203</v>
       </c>
       <c r="N3" t="n">
-        <v>96.45995121631046</v>
+        <v>96.45122638119551</v>
       </c>
       <c r="O3" t="n">
-        <v>9.821402711237864</v>
+        <v>9.820958526599911</v>
       </c>
       <c r="P3" t="n">
-        <v>386.8856100941272</v>
+        <v>386.8231760360276</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16156,7 +16212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D509"/>
+  <dimension ref="A1:D511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27357,6 +27413,50 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-35.00743400537518,173.77696273798153</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-35.007374139457895,173.77785805965362</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-35.00743059005627,173.77696240316132</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-35.007368117715025,173.77785746927083</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D511"/>
+  <dimension ref="A1:D513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9630,6 +9630,42 @@
       <c r="D511" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>401.09</v>
+      </c>
+      <c r="C512" t="n">
+        <v>402.56</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>400.86</v>
+      </c>
+      <c r="C513" t="n">
+        <v>402.32</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B626"/>
+  <dimension ref="A1:B628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15907,6 +15943,26 @@
       </c>
       <c r="B626" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -16075,28 +16131,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1309213533184835</v>
+        <v>0.1422856634423664</v>
       </c>
       <c r="J2" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0105056986892994</v>
+        <v>0.01234023964976538</v>
       </c>
       <c r="M2" t="n">
-        <v>8.565481048043436</v>
+        <v>8.608555530533966</v>
       </c>
       <c r="N2" t="n">
-        <v>103.1935048242156</v>
+        <v>103.9233491742756</v>
       </c>
       <c r="O2" t="n">
-        <v>10.15842039020908</v>
+        <v>10.19428021854783</v>
       </c>
       <c r="P2" t="n">
-        <v>380.3748252679683</v>
+        <v>380.2639717294376</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16153,28 +16209,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08880004966238128</v>
+        <v>0.09760013112541603</v>
       </c>
       <c r="J3" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005198739123882468</v>
+        <v>0.006274887016342157</v>
       </c>
       <c r="M3" t="n">
-        <v>8.24446545721203</v>
+        <v>8.274012614481206</v>
       </c>
       <c r="N3" t="n">
-        <v>96.45122638119551</v>
+        <v>96.75384636469397</v>
       </c>
       <c r="O3" t="n">
-        <v>9.820958526599911</v>
+        <v>9.836353306215367</v>
       </c>
       <c r="P3" t="n">
-        <v>386.8231760360276</v>
+        <v>386.7373354887843</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16212,7 +16268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D511"/>
+  <dimension ref="A1:D513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27457,6 +27513,50 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-35.007406053686175,173.77695999774323</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-35.00733746973996,173.77785446448817</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-35.00740812085288,173.77696020039744</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-35.007339626782205,173.7778546759684</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D513"/>
+  <dimension ref="A1:D516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9666,6 +9666,60 @@
       <c r="D513" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>401.36</v>
+      </c>
+      <c r="C514" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>403.19</v>
+      </c>
+      <c r="C515" t="n">
+        <v>401.83</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>403.8</v>
+      </c>
+      <c r="C516" t="n">
+        <v>402.36</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9680,7 +9734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B628"/>
+  <dimension ref="A1:B631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15963,6 +16017,36 @@
       </c>
       <c r="B628" t="n">
         <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -16131,28 +16215,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1422856634423664</v>
+        <v>0.1608093600645</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01234023964976538</v>
+        <v>0.01557976827033603</v>
       </c>
       <c r="M2" t="n">
-        <v>8.608555530533966</v>
+        <v>8.681461892720998</v>
       </c>
       <c r="N2" t="n">
-        <v>103.9233491742756</v>
+        <v>105.3333468657121</v>
       </c>
       <c r="O2" t="n">
-        <v>10.19428021854783</v>
+        <v>10.26320353816059</v>
       </c>
       <c r="P2" t="n">
-        <v>380.2639717294376</v>
+        <v>380.0821493341105</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16209,28 +16293,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09760013112541603</v>
+        <v>0.1103522058084597</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006274887016342157</v>
+        <v>0.008016368910492511</v>
       </c>
       <c r="M3" t="n">
-        <v>8.274012614481206</v>
+        <v>8.313859417457328</v>
       </c>
       <c r="N3" t="n">
-        <v>96.75384636469397</v>
+        <v>97.14323174557825</v>
       </c>
       <c r="O3" t="n">
-        <v>9.836353306215367</v>
+        <v>9.856126609656465</v>
       </c>
       <c r="P3" t="n">
-        <v>386.7373354887843</v>
+        <v>386.6121777534997</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16268,7 +16352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D513"/>
+  <dimension ref="A1:D516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27557,6 +27641,72 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-35.007403627012195,173.77695975984483</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-35.00733791912376,173.77785450854654</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-35.007387179555195,173.7769581474227</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-35.00734403074345,173.77785510774055</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-35.00738169706952,173.77695760994885</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-35.007339267275164,173.7778546407217</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D516"/>
+  <dimension ref="A1:D519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9718,6 +9718,60 @@
         <v>402.36</v>
       </c>
       <c r="D516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>404.46</v>
+      </c>
+      <c r="C517" t="n">
+        <v>402.41</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>405.6</v>
+      </c>
+      <c r="C518" t="n">
+        <v>402.72</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>406.89</v>
+      </c>
+      <c r="C519" t="n">
+        <v>403.53</v>
+      </c>
+      <c r="D519" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9734,7 +9788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B631"/>
+  <dimension ref="A1:B634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16047,6 +16101,36 @@
       </c>
       <c r="B631" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -16215,28 +16299,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1608093600645</v>
+        <v>0.1816403585611072</v>
       </c>
       <c r="J2" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K2" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01557976827033603</v>
+        <v>0.01953190506044955</v>
       </c>
       <c r="M2" t="n">
-        <v>8.681461892720998</v>
+        <v>8.769619099535175</v>
       </c>
       <c r="N2" t="n">
-        <v>105.3333468657121</v>
+        <v>107.3063972665092</v>
       </c>
       <c r="O2" t="n">
-        <v>10.26320353816059</v>
+        <v>10.35888011642712</v>
       </c>
       <c r="P2" t="n">
-        <v>380.0821493341105</v>
+        <v>379.8768631265553</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16293,28 +16377,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1103522058084597</v>
+        <v>0.1234028165256312</v>
       </c>
       <c r="J3" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K3" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008016368910492511</v>
+        <v>0.01000857629433671</v>
       </c>
       <c r="M3" t="n">
-        <v>8.313859417457328</v>
+        <v>8.35487852927513</v>
       </c>
       <c r="N3" t="n">
-        <v>97.14323174557825</v>
+        <v>97.5935967418617</v>
       </c>
       <c r="O3" t="n">
-        <v>9.856126609656465</v>
+        <v>9.878947147437408</v>
       </c>
       <c r="P3" t="n">
-        <v>386.6121777534997</v>
+        <v>386.483567717115</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16352,7 +16436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D516"/>
+  <dimension ref="A1:D519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27707,6 +27791,72 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-35.007375765199754,173.77695702841982</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-35.00733881789135,173.7778545966633</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-35.00736551924287,173.7769560239608</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-35.0073360317118,173.77785432350137</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-35.00735392513373,173.77695488733644</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-35.0073287516942,173.77785360975574</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D519"/>
+  <dimension ref="A1:D523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9772,6 +9772,78 @@
         <v>403.53</v>
       </c>
       <c r="D519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>406.85</v>
+      </c>
+      <c r="C520" t="n">
+        <v>403.16</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>408.08</v>
+      </c>
+      <c r="C521" t="n">
+        <v>403.23</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>409.51</v>
+      </c>
+      <c r="C522" t="n">
+        <v>404.97</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>410.99</v>
+      </c>
+      <c r="C523" t="n">
+        <v>406.76</v>
+      </c>
+      <c r="D523" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9788,7 +9860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B634"/>
+  <dimension ref="A1:B638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16131,6 +16203,46 @@
       </c>
       <c r="B634" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -16299,28 +16411,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1816403585611072</v>
+        <v>0.2126828399452503</v>
       </c>
       <c r="J2" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="K2" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01953190506044955</v>
+        <v>0.02592225368191359</v>
       </c>
       <c r="M2" t="n">
-        <v>8.769619099535175</v>
+        <v>8.907523471412429</v>
       </c>
       <c r="N2" t="n">
-        <v>107.3063972665092</v>
+        <v>110.8600434252092</v>
       </c>
       <c r="O2" t="n">
-        <v>10.35888011642712</v>
+        <v>10.5290096127418</v>
       </c>
       <c r="P2" t="n">
-        <v>379.8768631265553</v>
+        <v>379.569482374099</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16377,28 +16489,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1234028165256312</v>
+        <v>0.1423772033914974</v>
       </c>
       <c r="J3" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="K3" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01000857629433671</v>
+        <v>0.01324601004870973</v>
       </c>
       <c r="M3" t="n">
-        <v>8.35487852927513</v>
+        <v>8.418781132982454</v>
       </c>
       <c r="N3" t="n">
-        <v>97.5935967418617</v>
+        <v>98.4904235020813</v>
       </c>
       <c r="O3" t="n">
-        <v>9.878947147437408</v>
+        <v>9.924234151917281</v>
       </c>
       <c r="P3" t="n">
-        <v>386.483567717115</v>
+        <v>386.2956799665113</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16436,7 +16548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D519"/>
+  <dimension ref="A1:D523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27857,6 +27969,94 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-35.007354284640996,173.77695492258061</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-35.00733207713435,173.77785393578768</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-35.007343229792724,173.77695383882283</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-35.00733144799702,173.77785387410594</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-35.00733037740808,173.7769525788447</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-35.007315809440705,173.77785234087494</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-35.00731707563933,173.7769512748118</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-35.007299721500516,173.77785076358626</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
